--- a/dataset/results/loo_12_models_summary.xlsx
+++ b/dataset/results/loo_12_models_summary.xlsx
@@ -483,10 +483,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I2">
-        <v>0.1036269603331069</v>
+        <v>0.1482524306654038</v>
       </c>
       <c r="J2">
-        <v>2.560805484301986</v>
+        <v>2.381018708504035</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,10 +515,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I3">
-        <v>0.2828448650022135</v>
+        <v>0.285300417332716</v>
       </c>
       <c r="J3">
-        <v>27.98684757638877</v>
+        <v>28.73126658225844</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,10 +547,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I4">
-        <v>0.1659501936652911</v>
+        <v>0.1657099939996745</v>
       </c>
       <c r="J4">
-        <v>1.376881164415077</v>
+        <v>1.48364838547472</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,10 +579,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I5">
-        <v>0.01034722466647509</v>
+        <v>0.01006031866684983</v>
       </c>
       <c r="J5">
-        <v>0.5132999577734551</v>
+        <v>0.4146196851852313</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -611,10 +611,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I6">
-        <v>0.125718929333137</v>
+        <v>0.1221732913327287</v>
       </c>
       <c r="J6">
-        <v>1.216806759768996</v>
+        <v>1.130361606958265</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -643,10 +643,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I7">
-        <v>0.006511808666497624</v>
+        <v>0.007086148667440284</v>
       </c>
       <c r="J7">
-        <v>0.7356977034048838</v>
+        <v>0.7941736814963511</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -675,10 +675,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I8">
-        <v>0.0843511310001001</v>
+        <v>0.0938511073339517</v>
       </c>
       <c r="J8">
-        <v>12.57564115673761</v>
+        <v>12.49371428621337</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -707,10 +707,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I9">
-        <v>0.09315849833243799</v>
+        <v>0.1088502193330593</v>
       </c>
       <c r="J9">
-        <v>1.406375212181523</v>
+        <v>1.461830145078183</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -739,10 +739,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I10">
-        <v>0.07849468333370169</v>
+        <v>0.07712007699956303</v>
       </c>
       <c r="J10">
-        <v>0.9649897962851176</v>
+        <v>1.036365858521849</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -771,10 +771,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I11">
-        <v>0.1205698403330947</v>
+        <v>0.115833208332333</v>
       </c>
       <c r="J11">
-        <v>13.93287266105259</v>
+        <v>13.50657759439546</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -803,10 +803,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I12">
-        <v>0.006803210333600873</v>
+        <v>0.00742090533337129</v>
       </c>
       <c r="J12">
-        <v>0.6823835037164603</v>
+        <v>0.7015042524317261</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -835,10 +835,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I13">
-        <v>0.1474483639988951</v>
+        <v>0.1581810393327032</v>
       </c>
       <c r="J13">
-        <v>0.7406494473086865</v>
+        <v>0.7452064202422296</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models_summary.xlsx
+++ b/dataset/results/loo_12_models_summary.xlsx
@@ -483,10 +483,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I2">
-        <v>0.1482524306654038</v>
+        <v>0.1451409249990926</v>
       </c>
       <c r="J2">
-        <v>2.381018708504035</v>
+        <v>2.447597575972358</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,10 +515,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I3">
-        <v>0.285300417332716</v>
+        <v>0.2865156686663492</v>
       </c>
       <c r="J3">
-        <v>28.73126658225844</v>
+        <v>29.06318091121722</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,10 +547,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I4">
-        <v>0.1657099939996745</v>
+        <v>0.166257664332079</v>
       </c>
       <c r="J4">
-        <v>1.48364838547472</v>
+        <v>1.248580782371732</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,10 +579,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I5">
-        <v>0.01006031866684983</v>
+        <v>0.009478372667217627</v>
       </c>
       <c r="J5">
-        <v>0.4146196851852313</v>
+        <v>0.4203127121270102</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -611,10 +611,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I6">
-        <v>0.1221732913327287</v>
+        <v>0.1241626693336002</v>
       </c>
       <c r="J6">
-        <v>1.130361606958265</v>
+        <v>1.109312499781425</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -643,10 +643,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I7">
-        <v>0.007086148667440284</v>
+        <v>0.006172876665611208</v>
       </c>
       <c r="J7">
-        <v>0.7941736814963511</v>
+        <v>0.6784360121069817</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -675,10 +675,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I8">
-        <v>0.0938511073339517</v>
+        <v>0.08619219366664765</v>
       </c>
       <c r="J8">
-        <v>12.49371428621337</v>
+        <v>13.03370089274159</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -707,10 +707,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I9">
-        <v>0.1088502193330593</v>
+        <v>0.1891786829995302</v>
       </c>
       <c r="J9">
-        <v>1.461830145078183</v>
+        <v>1.541271470988763</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -739,10 +739,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I10">
-        <v>0.07712007699956303</v>
+        <v>0.07789974700062885</v>
       </c>
       <c r="J10">
-        <v>1.036365858521849</v>
+        <v>1.132674533189758</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -771,10 +771,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I11">
-        <v>0.115833208332333</v>
+        <v>0.1238632120002876</v>
       </c>
       <c r="J11">
-        <v>13.50657759439546</v>
+        <v>14.10902763580168</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -803,10 +803,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I12">
-        <v>0.00742090533337129</v>
+        <v>0.007472532334456143</v>
       </c>
       <c r="J12">
-        <v>0.7015042524317261</v>
+        <v>0.7018684107074447</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -835,10 +835,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I13">
-        <v>0.1581810393327032</v>
+        <v>0.1789946423341462</v>
       </c>
       <c r="J13">
-        <v>0.7452064202422296</v>
+        <v>0.7763892426737584</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models_summary.xlsx
+++ b/dataset/results/loo_12_models_summary.xlsx
@@ -483,10 +483,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I2">
-        <v>0.1451409249990926</v>
+        <v>0.1702051366664818</v>
       </c>
       <c r="J2">
-        <v>2.447597575972358</v>
+        <v>2.556464710865146</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,10 +515,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I3">
-        <v>0.2865156686663492</v>
+        <v>0.2749378509997769</v>
       </c>
       <c r="J3">
-        <v>29.06318091121722</v>
+        <v>27.9137967685974</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,10 +547,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I4">
-        <v>0.166257664332079</v>
+        <v>0.1646726350002913</v>
       </c>
       <c r="J4">
-        <v>1.248580782371732</v>
+        <v>1.364061649435665</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,10 +579,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I5">
-        <v>0.009478372667217627</v>
+        <v>0.009001148666963369</v>
       </c>
       <c r="J5">
-        <v>0.4203127121270102</v>
+        <v>0.4230769557697614</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -611,10 +611,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I6">
-        <v>0.1241626693336002</v>
+        <v>0.1239167423336767</v>
       </c>
       <c r="J6">
-        <v>1.109312499781425</v>
+        <v>1.849521258624801</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -643,10 +643,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I7">
-        <v>0.006172876665611208</v>
+        <v>0.006954325666811201</v>
       </c>
       <c r="J7">
-        <v>0.6784360121069817</v>
+        <v>0.7839581206123704</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -675,10 +675,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I8">
-        <v>0.08619219366664765</v>
+        <v>0.09631726733338535</v>
       </c>
       <c r="J8">
-        <v>13.03370089274159</v>
+        <v>12.920346938588</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -707,10 +707,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I9">
-        <v>0.1891786829995302</v>
+        <v>0.1026826980002322</v>
       </c>
       <c r="J9">
-        <v>1.541271470988763</v>
+        <v>1.413612457494013</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -739,10 +739,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I10">
-        <v>0.07789974700062885</v>
+        <v>0.07754363999993075</v>
       </c>
       <c r="J10">
-        <v>1.132674533189758</v>
+        <v>1.173045280684535</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -771,10 +771,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I11">
-        <v>0.1238632120002876</v>
+        <v>0.1153452609996748</v>
       </c>
       <c r="J11">
-        <v>14.10902763580168</v>
+        <v>13.1253071855303</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -803,10 +803,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I12">
-        <v>0.007472532334456143</v>
+        <v>0.01451095133355314</v>
       </c>
       <c r="J12">
-        <v>0.7018684107074447</v>
+        <v>0.678130952425762</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -835,10 +835,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I13">
-        <v>0.1789946423341462</v>
+        <v>0.1419320076662795</v>
       </c>
       <c r="J13">
-        <v>0.7763892426737584</v>
+        <v>0.7324313351617303</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models_summary.xlsx
+++ b/dataset/results/loo_12_models_summary.xlsx
@@ -483,10 +483,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I2">
-        <v>0.1702051366664818</v>
+        <v>0.1079688043331165</v>
       </c>
       <c r="J2">
-        <v>2.556464710865146</v>
+        <v>2.453133078199776</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,10 +515,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I3">
-        <v>0.2749378509997769</v>
+        <v>0.2748403593335145</v>
       </c>
       <c r="J3">
-        <v>27.9137967685974</v>
+        <v>27.98195344387002</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,10 +547,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I4">
-        <v>0.1646726350002913</v>
+        <v>0.1624036259994076</v>
       </c>
       <c r="J4">
-        <v>1.364061649435665</v>
+        <v>1.483711096913182</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,10 +579,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I5">
-        <v>0.009001148666963369</v>
+        <v>0.00973737433378119</v>
       </c>
       <c r="J5">
-        <v>0.4230769557697614</v>
+        <v>0.4459555695427057</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -611,10 +611,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I6">
-        <v>0.1239167423336767</v>
+        <v>0.1217973726664544</v>
       </c>
       <c r="J6">
-        <v>1.849521258624801</v>
+        <v>2.434784650962634</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -643,10 +643,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I7">
-        <v>0.006954325666811201</v>
+        <v>0.007778272333477314</v>
       </c>
       <c r="J7">
-        <v>0.7839581206123704</v>
+        <v>0.8782801870085901</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -675,10 +675,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I8">
-        <v>0.09631726733338535</v>
+        <v>0.09233422066669543</v>
       </c>
       <c r="J8">
-        <v>12.920346938588</v>
+        <v>12.58442006826731</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -707,10 +707,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I9">
-        <v>0.1026826980002322</v>
+        <v>0.1016046910008299</v>
       </c>
       <c r="J9">
-        <v>1.413612457494013</v>
+        <v>1.44539774669438</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -739,10 +739,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I10">
-        <v>0.07754363999993075</v>
+        <v>0.07725190300031197</v>
       </c>
       <c r="J10">
-        <v>1.173045280684535</v>
+        <v>1.565897321529674</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -771,10 +771,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I11">
-        <v>0.1153452609996748</v>
+        <v>0.1190006433340993</v>
       </c>
       <c r="J11">
-        <v>13.1253071855303</v>
+        <v>13.09620408243731</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -803,10 +803,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I12">
-        <v>0.01451095133355314</v>
+        <v>0.0211261180005143</v>
       </c>
       <c r="J12">
-        <v>0.678130952425762</v>
+        <v>0.6950248721945432</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -835,10 +835,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I13">
-        <v>0.1419320076662795</v>
+        <v>0.1256990220002384</v>
       </c>
       <c r="J13">
-        <v>0.7324313351617303</v>
+        <v>0.7692623292772079</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models_summary.xlsx
+++ b/dataset/results/loo_12_models_summary.xlsx
@@ -483,10 +483,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I2">
-        <v>0.1079688043331165</v>
+        <v>0.1558425820003322</v>
       </c>
       <c r="J2">
-        <v>2.453133078199776</v>
+        <v>3.122043154553776</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -515,10 +515,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I3">
-        <v>0.2748403593335145</v>
+        <v>0.2838168606661687</v>
       </c>
       <c r="J3">
-        <v>27.98195344387002</v>
+        <v>28.57940901290918</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -547,10 +547,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I4">
-        <v>0.1624036259994076</v>
+        <v>0.1646930569998707</v>
       </c>
       <c r="J4">
-        <v>1.483711096913182</v>
+        <v>1.279697065521239</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -579,10 +579,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I5">
-        <v>0.00973737433378119</v>
+        <v>0.009754442999110324</v>
       </c>
       <c r="J5">
-        <v>0.4459555695427057</v>
+        <v>0.460725977725716</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -611,10 +611,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I6">
-        <v>0.1217973726664544</v>
+        <v>0.1234546010006549</v>
       </c>
       <c r="J6">
-        <v>2.434784650962634</v>
+        <v>1.161884991072956</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -643,10 +643,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I7">
-        <v>0.007778272333477314</v>
+        <v>0.007154758666729322</v>
       </c>
       <c r="J7">
-        <v>0.8782801870085901</v>
+        <v>0.7473273812212603</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -675,10 +675,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I8">
-        <v>0.09233422066669543</v>
+        <v>0.0989725449993178</v>
       </c>
       <c r="J8">
-        <v>12.58442006826731</v>
+        <v>12.40933099578716</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -707,10 +707,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I9">
-        <v>0.1016046910008299</v>
+        <v>0.1283743346684787</v>
       </c>
       <c r="J9">
-        <v>1.44539774669438</v>
+        <v>1.59960267855964</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -739,10 +739,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I10">
-        <v>0.07725190300031197</v>
+        <v>0.07702573666513975</v>
       </c>
       <c r="J10">
-        <v>1.565897321529674</v>
+        <v>0.923535076501238</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -771,10 +771,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I11">
-        <v>0.1190006433340993</v>
+        <v>0.105059325665934</v>
       </c>
       <c r="J11">
-        <v>13.09620408243731</v>
+        <v>13.35195599485629</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -803,10 +803,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I12">
-        <v>0.0211261180005143</v>
+        <v>0.006587784000051518</v>
       </c>
       <c r="J12">
-        <v>0.6950248721945432</v>
+        <v>0.6465116916378789</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -835,10 +835,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I13">
-        <v>0.1256990220002384</v>
+        <v>0.1822000336651399</v>
       </c>
       <c r="J13">
-        <v>0.7692623292772079</v>
+        <v>0.7360178563672258</v>
       </c>
     </row>
   </sheetData>
